--- a/04_приложения_и_реестры/INTERNATIONAL_PRACTICES.xlsx
+++ b/04_приложения_и_реестры/INTERNATIONAL_PRACTICES.xlsx
@@ -448,7 +448,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G44"/>
+  <dimension ref="A1:G45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -2088,6 +2088,43 @@
         </is>
       </c>
     </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>I-easyread</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>Великобритания: Accessible Information Standard — информация для пациентов с нарушениями предоставляется в доступных форматах (включая easy read: короткие фразы + изображения); Mencap — методические материалы</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>NHS England / Mencap, Великобритания</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>https://www.mencap.org.uk/help-and-advice/health/accessible-information-standard</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>проверено 17.08.2026</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>глава 15, приложение 38 (памятка easy read)</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:G44"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
